--- a/static/pages/course_dv/dv30-visualperception/chart-source.xlsx
+++ b/static/pages/course_dv/dv30-visualperception/chart-source.xlsx
@@ -1,26 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ndg00008/Library/CloudStorage/Dropbox/Obsidian/courses/course_dv/dv35-visual-perception/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ndg00008/Documents/profgarrett/jsgames/static/pages/course_dv/dv30-visualperception/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC12391-9CA7-9F49-8F07-708B9C9C3DFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{294CB264-07EC-5944-9287-2939DF7E5711}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-61300" yWindow="-3960" windowWidth="28600" windowHeight="22140" xr2:uid="{63643A24-ED70-7744-842A-51F551DEBCFF}"/>
+    <workbookView xWindow="51920" yWindow="-7240" windowWidth="38240" windowHeight="20840" activeTab="2" xr2:uid="{63643A24-ED70-7744-842A-51F551DEBCFF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="table" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">Sheet1!$A$30:$A$32</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">Sheet1!$C$29</definedName>
-    <definedName name="_xlchart.v1.2" hidden="1">Sheet1!$C$30:$C$32</definedName>
-  </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -41,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="37">
   <si>
     <t>Start</t>
   </si>
@@ -69,12 +66,100 @@
   <si>
     <t>Change in Sales from Year 1</t>
   </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>December</t>
+  </si>
+  <si>
+    <t>Region A</t>
+  </si>
+  <si>
+    <t>Region B</t>
+  </si>
+  <si>
+    <t>Region C</t>
+  </si>
+  <si>
+    <t>Region D</t>
+  </si>
+  <si>
+    <t>Region E</t>
+  </si>
+  <si>
+    <t>Region F</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Nevada</t>
+  </si>
+  <si>
+    <t>West Virginia</t>
+  </si>
+  <si>
+    <t>(East) Virginia</t>
+  </si>
+  <si>
+    <t>California</t>
+  </si>
+  <si>
+    <t>Sales Tax</t>
+  </si>
+  <si>
+    <t>Owed</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Grown</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.0_);[Red]\(&quot;$&quot;#,##0.0\)"/>
+  </numFmts>
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -82,13 +167,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -103,9 +214,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -365,6 +482,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -372,7 +490,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -683,6 +800,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -690,7 +808,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -997,6 +1114,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1004,7 +1122,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1281,6 +1398,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1288,7 +1406,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1301,6 +1418,3151 @@
           <a:lumOff val="85000"/>
         </a:schemeClr>
       </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region A</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$4:$B$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>73</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8A7B-2A40-A0B3-0BF3DB334BD2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region B</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$4:$C$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-8A7B-2A40-A0B3-0BF3DB334BD2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$D$4:$D$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>76</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-8A7B-2A40-A0B3-0BF3DB334BD2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region D</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$E$4:$E$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>82</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-8A7B-2A40-A0B3-0BF3DB334BD2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$F$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region E</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$F$4:$F$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-8A7B-2A40-A0B3-0BF3DB334BD2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$G$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region F</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$G$4:$G$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-8A7B-2A40-A0B3-0BF3DB334BD2}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1505700800"/>
+        <c:axId val="1505702592"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1505700800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1505702592"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1505702592"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1505700800"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="5.9977123912142563E-2"/>
+          <c:y val="4.0441176470588237E-2"/>
+          <c:w val="0.64528603398259432"/>
+          <c:h val="0.78361654701250583"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region A</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$4:$B$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>73</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7C7D-E942-A6AB-9B6331197753}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region B</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$4:$C$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-7C7D-E942-A6AB-9B6331197753}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$D$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$D$4:$D$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>43</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>53</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>59</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>57</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>76</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-7C7D-E942-A6AB-9B6331197753}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region D</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$E$4:$E$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>42</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>51</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>62</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>64</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>74</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>81</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>82</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-7C7D-E942-A6AB-9B6331197753}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="4"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$F$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region E</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$F$4:$F$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>31</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>47</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>56</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>58</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-7C7D-E942-A6AB-9B6331197753}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$G$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region F</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$G$4:$G$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>34</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>17</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>8</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-7C7D-E942-A6AB-9B6331197753}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1505700800"/>
+        <c:axId val="1505702592"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1505700800"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1505702592"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1505702592"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1505700800"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales are increasing for both regions</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.3458822372564199E-2"/>
+          <c:y val="0.31397159878108266"/>
+          <c:w val="0.87210688693044236"/>
+          <c:h val="0.28056654851073121"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region A</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$4:$B$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>73</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-6026-A14E-9C74-8A938D8F0DC9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region B</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$4:$C$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-6026-A14E-9C74-8A938D8F0DC9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region A</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$4:$B$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>73</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6026-A14E-9C74-8A938D8F0DC9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region B</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$4:$C$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-6026-A14E-9C74-8A938D8F0DC9}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1506079872"/>
+        <c:axId val="1506237888"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1506079872"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1506237888"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1506237888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1506079872"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.30160950032138678"/>
+          <c:y val="0.79351630303917542"/>
+          <c:w val="0.34168595348460562"/>
+          <c:h val="4.9009114086475423E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst/>
+  </c:chart>
+  <c:spPr>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Sales are increasing for both regions</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="3.9683486507180767E-3"/>
+          <c:y val="2.2859213643050678E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="9.3458822372564199E-2"/>
+          <c:y val="0.31397159878108266"/>
+          <c:w val="0.87210688693044236"/>
+          <c:h val="0.28056654851073121"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region A</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$B$4:$B$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>35</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>46</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>52</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>61</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>69</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>67</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>73</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-E8BF-844C-A204-DAD8DB8E08CB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Sheet2!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Region B</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:f>Sheet2!$A$4:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>January</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>February</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>March</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>April</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>May</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>June</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>July</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>August</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>September</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>October</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>November</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>December</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet2!$C$4:$C$15</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="12"/>
+                <c:pt idx="0">
+                  <c:v>28</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>32</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>48</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>54</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>66</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>83</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>93</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>97</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-E8BF-844C-A204-DAD8DB8E08CB}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1506079872"/>
+        <c:axId val="1506237888"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1506079872"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1506237888"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1506237888"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1506079872"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0"/>
+          <c:y val="0.77827682727714176"/>
+          <c:w val="0.34168595348460562"/>
+          <c:h val="4.9009114086475423E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -1483,6 +4745,126 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -3142,6 +6524,1554 @@
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
     <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
       <a:ln w="9525">
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3648,6 +8578,1360 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>12959</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>64796</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>427653</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>12959</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="Rectangle 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{27B64442-CCDF-37EB-655D-8D54F8476014}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="12959" y="7943980"/>
+          <a:ext cx="13684898" cy="6790612"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>311020</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>193092</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>762259</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>193092</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0DA21A65-7D8E-7CFB-735A-53C79E18275D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>596900</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>323979</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>165100</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CDC0F30-CF66-0941-8345-41FB5A759CC1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>660400</xdr:colOff>
+      <xdr:row>175</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{14DFDFC1-8CBB-2D64-61EF-D278C9D16010}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="40284400" y="35572700"/>
+          <a:ext cx="990600" cy="266700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>42</xdr:col>
+      <xdr:colOff>647700</xdr:colOff>
+      <xdr:row>151</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>152</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE2D34C9-1230-8F79-5D4C-E5094E29C184}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="35318700" y="30695900"/>
+          <a:ext cx="1028700" cy="254000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>36</xdr:col>
+      <xdr:colOff>635000</xdr:colOff>
+      <xdr:row>127</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>128</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A5521E4-80FF-B754-AC65-4F4F5F79628E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="30353000" y="25819100"/>
+          <a:ext cx="1143000" cy="228600"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>622300</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>812800</xdr:colOff>
+      <xdr:row>104</xdr:row>
+      <xdr:rowOff>88900</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDE242BA-8E0F-85DF-7C7E-78560DDDCFC6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="25387300" y="20942300"/>
+          <a:ext cx="1016000" cy="279400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>609600</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F34BA3F3-B363-054A-63D7-E66BCA3D1F88}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20421600" y="16065500"/>
+          <a:ext cx="939800" cy="254000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>795337</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>84138</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>160337</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>122238</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FC73DA30-FDF0-B277-0E0E-44EFEBC0187F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10701337" y="6481763"/>
+          <a:ext cx="1016000" cy="244475"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>723900</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>25400</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>169862</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3BB6504-ED94-0515-C219-374C7DDBF986}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10629900" y="5316537"/>
+          <a:ext cx="952500" cy="219075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>785813</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>6420</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>39309</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5452B38C-65EF-8E09-9088-4A43929BF50C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:srcRect l="3937" r="4275"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10691813" y="4340295"/>
+          <a:ext cx="904496" cy="279330"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>679450</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>158750</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>23813</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>166688</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{039D638D-B9EB-F387-7819-3C0CB70D33A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:srcRect t="1" r="3241" b="17681"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10585450" y="4699000"/>
+          <a:ext cx="995363" cy="214313"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>685801</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>25401</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E273365C-977E-3C6A-5416-CA70EF555BB0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10591801" y="5086350"/>
+          <a:ext cx="990600" cy="273050"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>717550</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>12701</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>166689</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD255032-4A12-F7C6-60A3-66DEB1360A0D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:srcRect b="33561"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="10623550" y="4965701"/>
+          <a:ext cx="1143000" cy="153988"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>208642</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>196460</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>764591</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>12959</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="16" name="Chart 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34BCCB7A-92D0-B456-E18A-BD65F2DCF641}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId10"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>609083</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>142552</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>505408</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>168470</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="TextBox 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{325E9205-4EFD-F398-5F9E-DBA47D97CDA2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="609083" y="8851123"/>
+          <a:ext cx="4872652" cy="855306"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400"/>
+            <a:t>Our sales have</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" baseline="0"/>
+            <a:t> benefited from several strong sales quarters. The largest customers are growing very dependent on our supplies scheduling. We need to grow production as a result.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>165361</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>155509</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>505408</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>61684</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="TextBox 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0FE3953-3DF8-E944-B25B-6D309CA5628B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="165361" y="12803672"/>
+          <a:ext cx="5316374" cy="320869"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400"/>
+            <a:t>Source: Sales db 4/7 Export</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>555949</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>23845</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="19" name="Chart 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ECC1D96A-D14F-C34E-9B18-AB03B2449B3D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>829387</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>129591</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>466529</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>51836</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="TextBox 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{839F7FAB-5C37-104D-8217-39CD1027EA06}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6635101" y="9045509"/>
+          <a:ext cx="5442857" cy="751633"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400"/>
+            <a:t>Our sales have</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400" baseline="0"/>
+            <a:t> benefited from several strong sales quarters. The largest customers are growing very dependent on our supplies scheduling. We need to grow production as a result.</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>80</xdr:row>
+      <xdr:rowOff>25917</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>340047</xdr:colOff>
+      <xdr:row>81</xdr:row>
+      <xdr:rowOff>139439</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="TextBox 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2E246B13-E644-524C-B9F3-060B152291E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5805714" y="16613672"/>
+          <a:ext cx="5316374" cy="320869"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400"/>
+            <a:t>Source: Sales db 4/7 Export</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>77754</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>51837</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>417802</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>165359</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="TextBox 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{40759D40-D96D-A840-9E71-C952D868B22D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5054081" y="13114694"/>
+          <a:ext cx="5316374" cy="320869"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400"/>
+            <a:t>Source: Sales db 4/7 Export</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>777551</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>168468</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>790510</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>77755</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="26" name="Straight Connector 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B0B8BB1-7601-4C3F-94C7-C2D16A770DD2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1606939" y="8462346"/>
+          <a:ext cx="12959" cy="738674"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>657809</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>100563</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>670768</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>9849</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="28" name="Straight Connector 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5857926-A92C-2440-86CA-C5B261375712}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="657809" y="8809134"/>
+          <a:ext cx="12959" cy="738674"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>343678</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>58575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>356637</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>175208</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="30" name="Straight Connector 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9DD1960-0EFE-5C4E-89EB-C16C4FAD0938}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="2002454" y="12084697"/>
+          <a:ext cx="12959" cy="738674"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>68425</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>185057</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>81384</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>94343</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="31" name="Straight Connector 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7D67EA1E-B7A5-D648-ACB1-6A9D8378902C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="1727201" y="12625873"/>
+          <a:ext cx="12959" cy="738674"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>285102</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>156028</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>285622</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>103673</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="32" name="Straight Connector 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C4EAA2D-8D45-CA4A-AE47-ABDCECC1C776}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="285102" y="9901334"/>
+          <a:ext cx="520" cy="1813768"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>38878</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>3628</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>42508</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>90715</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="35" name="Straight Connector 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A655296E-9B97-1544-BA44-19F1F3D9DF47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipH="1">
+          <a:off x="6673980" y="8504852"/>
+          <a:ext cx="3630" cy="5063414"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="57150"/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent5"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent5"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent5"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -4067,4 +10351,490 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83BB1A93-7848-914A-AD79-A227ECD52C5A}">
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B1">
+        <v>1</v>
+      </c>
+      <c r="C1">
+        <v>3</v>
+      </c>
+      <c r="D1">
+        <v>1</v>
+      </c>
+      <c r="E1">
+        <v>-2</v>
+      </c>
+      <c r="F1">
+        <v>0</v>
+      </c>
+      <c r="G1">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>30</v>
+      </c>
+      <c r="C4">
+        <v>28</v>
+      </c>
+      <c r="D4">
+        <v>37</v>
+      </c>
+      <c r="E4">
+        <v>36</v>
+      </c>
+      <c r="F4">
+        <v>20</v>
+      </c>
+      <c r="G4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>35</v>
+      </c>
+      <c r="C5">
+        <v>32</v>
+      </c>
+      <c r="D5">
+        <v>36</v>
+      </c>
+      <c r="E5">
+        <v>42</v>
+      </c>
+      <c r="F5">
+        <v>17</v>
+      </c>
+      <c r="G5">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>36</v>
+      </c>
+      <c r="C6">
+        <v>41</v>
+      </c>
+      <c r="D6">
+        <v>42</v>
+      </c>
+      <c r="E6">
+        <v>44</v>
+      </c>
+      <c r="F6">
+        <v>24</v>
+      </c>
+      <c r="G6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
+        <v>38</v>
+      </c>
+      <c r="C7">
+        <v>48</v>
+      </c>
+      <c r="D7">
+        <v>43</v>
+      </c>
+      <c r="E7">
+        <v>51</v>
+      </c>
+      <c r="F7">
+        <v>31</v>
+      </c>
+      <c r="G7">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>48</v>
+      </c>
+      <c r="C8">
+        <v>54</v>
+      </c>
+      <c r="D8">
+        <v>43</v>
+      </c>
+      <c r="E8">
+        <v>54</v>
+      </c>
+      <c r="F8">
+        <v>32</v>
+      </c>
+      <c r="G8">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>46</v>
+      </c>
+      <c r="C9">
+        <v>66</v>
+      </c>
+      <c r="D9">
+        <v>53</v>
+      </c>
+      <c r="E9">
+        <v>56</v>
+      </c>
+      <c r="F9">
+        <v>30</v>
+      </c>
+      <c r="G9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10">
+        <v>50</v>
+      </c>
+      <c r="C10">
+        <v>78</v>
+      </c>
+      <c r="D10">
+        <v>59</v>
+      </c>
+      <c r="E10">
+        <v>62</v>
+      </c>
+      <c r="F10">
+        <v>38</v>
+      </c>
+      <c r="G10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11">
+        <v>52</v>
+      </c>
+      <c r="C11">
+        <v>83</v>
+      </c>
+      <c r="D11">
+        <v>57</v>
+      </c>
+      <c r="E11">
+        <v>64</v>
+      </c>
+      <c r="F11">
+        <v>47</v>
+      </c>
+      <c r="G11">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12">
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>93</v>
+      </c>
+      <c r="D12">
+        <v>67</v>
+      </c>
+      <c r="E12">
+        <v>70</v>
+      </c>
+      <c r="F12">
+        <v>46</v>
+      </c>
+      <c r="G12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>69</v>
+      </c>
+      <c r="C13">
+        <v>97</v>
+      </c>
+      <c r="D13">
+        <v>74</v>
+      </c>
+      <c r="E13">
+        <v>74</v>
+      </c>
+      <c r="F13">
+        <v>56</v>
+      </c>
+      <c r="G13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14">
+        <v>67</v>
+      </c>
+      <c r="C14">
+        <v>97</v>
+      </c>
+      <c r="D14">
+        <v>77</v>
+      </c>
+      <c r="E14">
+        <v>81</v>
+      </c>
+      <c r="F14">
+        <v>58</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15">
+        <v>73</v>
+      </c>
+      <c r="C15">
+        <v>100</v>
+      </c>
+      <c r="D15">
+        <v>76</v>
+      </c>
+      <c r="E15">
+        <v>82</v>
+      </c>
+      <c r="F15">
+        <v>60</v>
+      </c>
+      <c r="G15">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6A43FAC-5EE3-9C48-B878-ECD143CD7EFC}">
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="14.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="22" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="2">
+        <v>2398</v>
+      </c>
+      <c r="C2" s="3">
+        <f>B2*0.04</f>
+        <v>95.92</v>
+      </c>
+      <c r="D2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B3" s="2">
+        <v>2823</v>
+      </c>
+      <c r="C3" s="3">
+        <f t="shared" ref="C3:C5" si="0">B3*0.04</f>
+        <v>112.92</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>30</v>
+      </c>
+      <c r="B4" s="2">
+        <v>84</v>
+      </c>
+      <c r="C4" s="3">
+        <f t="shared" si="0"/>
+        <v>3.36</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="2">
+        <v>837</v>
+      </c>
+      <c r="C5" s="3">
+        <f t="shared" si="0"/>
+        <v>33.480000000000004</v>
+      </c>
+      <c r="D5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="C2:C5">
+    <cfRule type="dataBar" priority="4">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF638EC6"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{C7E9B716-B3E2-1B4E-ACDD-3B6D83BAB2B9}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B2:B5">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E2:E5">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="5Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="20"/>
+        <cfvo type="percent" val="40"/>
+        <cfvo type="percent" val="60"/>
+        <cfvo type="percent" val="80"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{C7E9B716-B3E2-1B4E-ACDD-3B6D83BAB2B9}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF638EC6"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>C2:C5</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
 </file>